--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0003T0006Z000C1N10_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0003T0006Z000C1N10_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>34.58802206776158</v>
+        <v>5.620553586011257</v>
       </c>
       <c r="D2" t="n">
-        <v>34.80512436378056</v>
+        <v>5.655832709114341</v>
       </c>
       <c r="E2" t="n">
-        <v>4.286521988471385</v>
+        <v>0.6965598231266004</v>
       </c>
       <c r="F2" t="n">
-        <v>1.743799520921105</v>
+        <v>0.2833674221496794</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>43.16106604470435</v>
+        <v>7.013673232264457</v>
       </c>
       <c r="D3" t="n">
-        <v>31.31752532193835</v>
+        <v>5.089097864814982</v>
       </c>
       <c r="E3" t="n">
-        <v>4.286521988471385</v>
+        <v>0.6965598231266004</v>
       </c>
       <c r="F3" t="n">
-        <v>1.743799520921105</v>
+        <v>0.2833674221496794</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
